--- a/datasets/resultados.xlsx
+++ b/datasets/resultados.xlsx
@@ -1,52 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +267,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,285 +402,283 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Unnamed: 0</v>
-      </c>
-      <c r="B1" t="str">
-        <v>W0-inicial</v>
-      </c>
-      <c r="C1" t="str">
-        <v>W1-inicial</v>
-      </c>
-      <c r="D1" t="str">
-        <v>W2-inicial</v>
-      </c>
-      <c r="E1" t="str">
-        <v>W3-inicial</v>
-      </c>
-      <c r="F1" t="str">
-        <v>W4-inicial</v>
-      </c>
-      <c r="G1" t="str">
-        <v>W0-final</v>
-      </c>
-      <c r="H1" t="str">
-        <v>W1-final</v>
-      </c>
-      <c r="I1" t="str">
-        <v>W2-final</v>
-      </c>
-      <c r="J1" t="str">
-        <v>W3-final</v>
-      </c>
-      <c r="K1" t="str">
-        <v>W4-final</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Numero-de-epocas</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>W0-inicial</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>W1-inicial</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>W2-inicial</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>W3-inicial</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>W4-inicial</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>W0-final</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>W1-final</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>W2-final</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>W3-final</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>W4-final</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Numero-de-epocas</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>T1_x000d_</v>
-      </c>
-      <c r="B2" t="str">
-        <v>0.018197473</v>
-      </c>
-      <c r="C2" t="str">
-        <v>0.993891759</v>
-      </c>
-      <c r="D2" t="str">
-        <v>-0.736484004</v>
-      </c>
-      <c r="E2" t="str">
-        <v>0.500430683</v>
-      </c>
-      <c r="F2" t="str">
-        <v>-17.50456932</v>
-      </c>
-      <c r="G2" t="str">
-        <v>-74.98180253</v>
-      </c>
-      <c r="H2" t="str">
-        <v>37.75889176</v>
-      </c>
-      <c r="I2" t="str">
-        <v>61.273516</v>
-      </c>
-      <c r="J2" t="str">
-        <v>-17.50456932</v>
-      </c>
-      <c r="K2" t="str">
-        <v>-17.50456932</v>
-      </c>
-      <c r="L2" t="str">
-        <v>393</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T1_x000d_</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9372282904412087</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0671035686893392</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.04012896316003933</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5282318807488501</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3213335534773027</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.054805498912199</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.03046199889988832</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2057834921748172</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4915595494267479</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1657201180659474</v>
+      </c>
+      <c r="L2" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>T2_x000d_</v>
-      </c>
-      <c r="B3" t="str">
-        <v>0.514486631</v>
-      </c>
-      <c r="C3" t="str">
-        <v>0.783787012</v>
-      </c>
-      <c r="D3" t="str">
-        <v>-0.519941223</v>
-      </c>
-      <c r="E3" t="str">
-        <v>-0.616243262</v>
-      </c>
-      <c r="F3" t="str">
-        <v>-17.68624326</v>
-      </c>
-      <c r="G3" t="str">
-        <v>-75.48551337</v>
-      </c>
-      <c r="H3" t="str">
-        <v>38.20378701</v>
-      </c>
-      <c r="I3" t="str">
-        <v>61.81505878</v>
-      </c>
-      <c r="J3" t="str">
-        <v>-17.68624326</v>
-      </c>
-      <c r="K3" t="str">
-        <v>-17.68624326</v>
-      </c>
-      <c r="L3" t="str">
-        <v>389</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T2_x000d_</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.5755046539379054</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2554302973445306</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8148647534111354</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4511569585647078</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05768439487700616</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5226460795465168</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2992923423745048</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7403923079511081</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4676435479173818</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.1276427180840091</v>
+      </c>
+      <c r="L3" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>T3_x000d_</v>
-      </c>
-      <c r="B4" t="str">
-        <v>-0.357650588</v>
-      </c>
-      <c r="C4" t="str">
-        <v>-0.513850924</v>
-      </c>
-      <c r="D4" t="str">
-        <v>0.016638451</v>
-      </c>
-      <c r="E4" t="str">
-        <v>0.673323411</v>
-      </c>
-      <c r="F4" t="str">
-        <v>-18.53667659</v>
-      </c>
-      <c r="G4" t="str">
-        <v>-77.35765059</v>
-      </c>
-      <c r="H4" t="str">
-        <v>40.17114908</v>
-      </c>
-      <c r="I4" t="str">
-        <v>63.20663845</v>
-      </c>
-      <c r="J4" t="str">
-        <v>-18.53667659</v>
-      </c>
-      <c r="K4" t="str">
-        <v>-18.53667659</v>
-      </c>
-      <c r="L4" t="str">
-        <v>422</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T3_x000d_</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.8478745261109886</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5075508625538205</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08177913671703063</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9140913998763719</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3654363410729643</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.06954519545848</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3236085411292717</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3940909427607118</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8449523181068898</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.07205521019155907</v>
+      </c>
+      <c r="L4" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>T4_x000d_</v>
-      </c>
-      <c r="B5" t="str">
-        <v>-0.34352421</v>
-      </c>
-      <c r="C5" t="str">
-        <v>0.81238641</v>
-      </c>
-      <c r="D5" t="str">
-        <v>0.920766934</v>
-      </c>
-      <c r="E5" t="str">
-        <v>-0.239385424</v>
-      </c>
-      <c r="F5" t="str">
-        <v>-17.16938542</v>
-      </c>
-      <c r="G5" t="str">
-        <v>-73.34352421</v>
-      </c>
-      <c r="H5" t="str">
-        <v>37.89238641</v>
-      </c>
-      <c r="I5" t="str">
-        <v>60.47076693</v>
-      </c>
-      <c r="J5" t="str">
-        <v>-17.16938542</v>
-      </c>
-      <c r="K5" t="str">
-        <v>-17.16938542</v>
-      </c>
-      <c r="L5" t="str">
-        <v>370</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T4_x000d_</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.626224579278285</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6966572340634268</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8632943052164544</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7116582611571106</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5893624522942055</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7592967256414169</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5862339670112996</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.050779652227472</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.67015305870645</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.4132414665825997</v>
+      </c>
+      <c r="L5" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>T5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>-0.912174943</v>
-      </c>
-      <c r="C6" t="str">
-        <v>0.870506968</v>
-      </c>
-      <c r="D6" t="str">
-        <v>-0.567383043</v>
-      </c>
-      <c r="E6" t="str">
-        <v>0.177375919</v>
-      </c>
-      <c r="F6" t="str">
-        <v>-18.26262408</v>
-      </c>
-      <c r="G6" t="str">
-        <v>-76.41217494</v>
-      </c>
-      <c r="H6" t="str">
-        <v>38.51550697</v>
-      </c>
-      <c r="I6" t="str">
-        <v>62.07761696</v>
-      </c>
-      <c r="J6" t="str">
-        <v>-18.26262408</v>
-      </c>
-      <c r="K6" t="str">
-        <v>-18.26262408</v>
-      </c>
-      <c r="L6" t="str">
-        <v>409</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9879661952200952</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1222838249491444</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7195162429259677</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5935405718499178</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9204340714826253</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.078576438875382</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0470954447639868</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8471770152119025</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5652792368538335</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.800511414004852</v>
+      </c>
+      <c r="L6" t="n">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/datasets/resultados.xlsx
+++ b/datasets/resultados.xlsx
@@ -485,37 +485,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9372282904412087</v>
+        <v>0.9800199203702846</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0671035686893392</v>
+        <v>0.9986591206774607</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04012896316003933</v>
+        <v>0.05509867422161274</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5282318807488501</v>
+        <v>0.07519537267078169</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3213335534773027</v>
+        <v>0.8419216368600818</v>
       </c>
       <c r="G2" t="n">
-        <v>1.054805498912199</v>
+        <v>1.324606756796656</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03046199889988832</v>
+        <v>0.7127209638108565</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2057834921748172</v>
+        <v>0.5405870680627293</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4915595494267479</v>
+        <v>-0.03228126161060403</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1657201180659474</v>
+        <v>0.3858609588497772</v>
       </c>
       <c r="L2" t="n">
-        <v>97</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3">
@@ -525,37 +525,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5755046539379054</v>
+        <v>0.8516333919190305</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2554302973445306</v>
+        <v>0.002815179406710611</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8148647534111354</v>
+        <v>0.6498141690005287</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4511569585647078</v>
+        <v>0.2128845103499536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05768439487700616</v>
+        <v>0.8119032053681473</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5226460795465168</v>
+        <v>0.918690726520914</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2992923423745048</v>
+        <v>-0.05282899684593236</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7403923079511081</v>
+        <v>0.744291247721123</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4676435479173818</v>
+        <v>0.1919693276876262</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1276427180840091</v>
+        <v>0.7231528230225549</v>
       </c>
       <c r="L3" t="n">
-        <v>83</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4">
@@ -565,37 +565,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8478745261109886</v>
+        <v>0.6368204916325527</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5075508625538205</v>
+        <v>0.6475233880639492</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08177913671703063</v>
+        <v>0.007963913085173857</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9140913998763719</v>
+        <v>0.9399615779529363</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3654363410729643</v>
+        <v>0.3548903539654203</v>
       </c>
       <c r="G4" t="n">
-        <v>1.06954519545848</v>
+        <v>0.934928413933756</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3236085411292717</v>
+        <v>0.4001534341384105</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3940909427607118</v>
+        <v>0.4279681648153393</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8449523181068898</v>
+        <v>0.8469817169871896</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07205521019155907</v>
+        <v>-0.03965548120022198</v>
       </c>
       <c r="L4" t="n">
-        <v>108</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5">
@@ -605,37 +605,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.626224579278285</v>
+        <v>0.816651454176589</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6966572340634268</v>
+        <v>0.5964914374808805</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8632943052164544</v>
+        <v>0.6547064067965587</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7116582611571106</v>
+        <v>0.3714269908761163</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5893624522942055</v>
+        <v>0.2218646066486727</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7592967256414169</v>
+        <v>0.845549140766961</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5862339670112996</v>
+        <v>0.57251213714819</v>
       </c>
       <c r="I5" t="n">
-        <v>1.050779652227472</v>
+        <v>0.6954203574337338</v>
       </c>
       <c r="J5" t="n">
-        <v>0.67015305870645</v>
+        <v>0.3624138024285792</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4132414665825997</v>
+        <v>0.1836185184463149</v>
       </c>
       <c r="L5" t="n">
-        <v>99</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6">
@@ -645,37 +645,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9879661952200952</v>
+        <v>0.8306410011399743</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1222838249491444</v>
+        <v>0.629184720201179</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7195162429259677</v>
+        <v>0.8020383488692475</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5935405718499178</v>
+        <v>0.7391775873639409</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9204340714826253</v>
+        <v>0.2608064498049328</v>
       </c>
       <c r="G6" t="n">
-        <v>1.078576438875382</v>
+        <v>0.8544249439629754</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0470954447639868</v>
+        <v>0.6094488044466531</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8471770152119025</v>
+        <v>0.8355475459125734</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5652792368538335</v>
+        <v>0.7317593755974462</v>
       </c>
       <c r="K6" t="n">
-        <v>0.800511414004852</v>
+        <v>0.2293284014786916</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/resultados.xlsx
+++ b/datasets/resultados.xlsx
@@ -485,37 +485,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9800199203702846</v>
+        <v>0.1801084109198433</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9986591206774607</v>
+        <v>0.3246263576665106</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05509867422161274</v>
+        <v>0.1321218307377507</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07519537267078169</v>
+        <v>0.7807759665776581</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8419216368600818</v>
+        <v>0.8477759117487647</v>
       </c>
       <c r="G2" t="n">
-        <v>1.324606756796656</v>
+        <v>-1.811371400729789</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7127209638108565</v>
+        <v>1.312594506287354</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5405870680627293</v>
+        <v>1.641438282318985</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.03228126161060403</v>
+        <v>-0.426450526824132</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3858609588497772</v>
+        <v>-1.177160309886814</v>
       </c>
       <c r="L2" t="n">
-        <v>417</v>
+        <v>908</v>
       </c>
     </row>
     <row r="3">
@@ -525,37 +525,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8516333919190305</v>
+        <v>0.144384282251052</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002815179406710611</v>
+        <v>0.5871982285562491</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6498141690005287</v>
+        <v>0.06067809057739937</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2128845103499536</v>
+        <v>0.7295971434504257</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8119032053681473</v>
+        <v>0.3398995787876072</v>
       </c>
       <c r="G3" t="n">
-        <v>0.918690726520914</v>
+        <v>-1.811337621847773</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.05282899684593236</v>
+        <v>1.312596637663936</v>
       </c>
       <c r="I3" t="n">
-        <v>0.744291247721123</v>
+        <v>1.641430846064108</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1919693276876262</v>
+        <v>-0.4264112563860544</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7231528230225549</v>
+        <v>-1.17715368596102</v>
       </c>
       <c r="L3" t="n">
-        <v>300</v>
+        <v>895</v>
       </c>
     </row>
     <row r="4">
@@ -565,37 +565,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6368204916325527</v>
+        <v>0.9433632253604249</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6475233880639492</v>
+        <v>0.4003879856485225</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007963913085173857</v>
+        <v>0.3770599178957899</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9399615779529363</v>
+        <v>0.7654588136516226</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3548903539654203</v>
+        <v>0.1875750663032257</v>
       </c>
       <c r="G4" t="n">
-        <v>0.934928413933756</v>
+        <v>-1.811325864036243</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4001534341384105</v>
+        <v>1.312629974796408</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4279681648153393</v>
+        <v>1.641469187573193</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8469817169871896</v>
+        <v>-0.4263328678270338</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.03965548120022198</v>
+        <v>-1.177175046533524</v>
       </c>
       <c r="L4" t="n">
-        <v>406</v>
+        <v>925</v>
       </c>
     </row>
     <row r="5">
@@ -605,37 +605,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.816651454176589</v>
+        <v>0.3466363811794463</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5964914374808805</v>
+        <v>0.4425871327790274</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6547064067965587</v>
+        <v>0.9336018082341273</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3714269908761163</v>
+        <v>0.001725087504652278</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2218646066486727</v>
+        <v>0.04358662349387843</v>
       </c>
       <c r="G5" t="n">
-        <v>0.845549140766961</v>
+        <v>-1.811381889365442</v>
       </c>
       <c r="H5" t="n">
-        <v>0.57251213714819</v>
+        <v>1.31254080990423</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6954203574337338</v>
+        <v>1.64137397559721</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3624138024285792</v>
+        <v>-0.4265680705821237</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1836185184463149</v>
+        <v>-1.177123848960075</v>
       </c>
       <c r="L5" t="n">
-        <v>241</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6">
@@ -645,37 +645,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8306410011399743</v>
+        <v>0.9813712424318564</v>
       </c>
       <c r="C6" t="n">
-        <v>0.629184720201179</v>
+        <v>0.1370530433438095</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8020383488692475</v>
+        <v>0.494042591850773</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7391775873639409</v>
+        <v>0.4582442168666381</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2608064498049328</v>
+        <v>0.1203877380022312</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8544249439629754</v>
+        <v>-1.811333447582505</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6094488044466531</v>
+        <v>1.312600244423219</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8355475459125734</v>
+        <v>1.641434124455509</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7317593755974462</v>
+        <v>-0.4263997673276244</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2293284014786916</v>
+        <v>-1.1771552943768</v>
       </c>
       <c r="L6" t="n">
-        <v>227</v>
+        <v>915</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/resultados.xlsx
+++ b/datasets/resultados.xlsx
@@ -485,37 +485,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1801084109198433</v>
+        <v>0.04289848953589559</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3246263576665106</v>
+        <v>0.1384538233415276</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1321218307377507</v>
+        <v>0.5971753034935263</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7807759665776581</v>
+        <v>0.2997400420060883</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8477759117487647</v>
+        <v>0.9051355529908324</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.811371400729789</v>
+        <v>-1.811403147204154</v>
       </c>
       <c r="H2" t="n">
-        <v>1.312594506287354</v>
+        <v>1.312533327780612</v>
       </c>
       <c r="I2" t="n">
-        <v>1.641438282318985</v>
+        <v>1.641370969343198</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.426450526824132</v>
+        <v>-0.4266049181231152</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.177160309886814</v>
+        <v>-1.177123572857835</v>
       </c>
       <c r="L2" t="n">
-        <v>908</v>
+        <v>874</v>
       </c>
     </row>
     <row r="3">
@@ -525,37 +525,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.144384282251052</v>
+        <v>0.3173566539875597</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5871982285562491</v>
+        <v>0.2868545494040374</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06067809057739937</v>
+        <v>0.787731605552535</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7295971434504257</v>
+        <v>0.2280676519740199</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3398995787876072</v>
+        <v>0.9628657425999365</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.811337621847773</v>
+        <v>-1.81125162409968</v>
       </c>
       <c r="H3" t="n">
-        <v>1.312596637663936</v>
+        <v>1.312527866998524</v>
       </c>
       <c r="I3" t="n">
-        <v>1.641430846064108</v>
+        <v>1.641318757223016</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4264112563860544</v>
+        <v>-0.4264585693889776</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.17715368596102</v>
+        <v>-1.177082957283175</v>
       </c>
       <c r="L3" t="n">
-        <v>895</v>
+        <v>880</v>
       </c>
     </row>
     <row r="4">
@@ -565,37 +565,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9433632253604249</v>
+        <v>0.3978402639193718</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4003879856485225</v>
+        <v>0.5620282189080513</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3770599178957899</v>
+        <v>0.8070161698698157</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7654588136516226</v>
+        <v>0.01899217805759756</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1875750663032257</v>
+        <v>0.9853537168065982</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.811325864036243</v>
+        <v>-1.811267786774996</v>
       </c>
       <c r="H4" t="n">
-        <v>1.312629974796408</v>
+        <v>1.312515061780266</v>
       </c>
       <c r="I4" t="n">
-        <v>1.641469187573193</v>
+        <v>1.641307488173511</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4263328678270338</v>
+        <v>-0.4265008269318374</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.177175046533524</v>
+        <v>-1.177077554027331</v>
       </c>
       <c r="L4" t="n">
-        <v>925</v>
+        <v>874</v>
       </c>
     </row>
     <row r="5">
@@ -605,37 +605,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3466363811794463</v>
+        <v>0.1059012921808319</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4425871327790274</v>
+        <v>0.6590455163622504</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9336018082341273</v>
+        <v>0.7297376894335139</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001725087504652278</v>
+        <v>0.6908461407020068</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04358662349387843</v>
+        <v>0.3366958750227624</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.811381889365442</v>
+        <v>-1.81136516003324</v>
       </c>
       <c r="H5" t="n">
-        <v>1.31254080990423</v>
+        <v>1.31263028301746</v>
       </c>
       <c r="I5" t="n">
-        <v>1.64137397559721</v>
+        <v>1.64148134186789</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4265680705821237</v>
+        <v>-0.4263730102491579</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.177123848960075</v>
+        <v>-1.177184778043431</v>
       </c>
       <c r="L5" t="n">
-        <v>848</v>
+        <v>873</v>
       </c>
     </row>
     <row r="6">
@@ -645,37 +645,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9813712424318564</v>
+        <v>0.06357839535486198</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1370530433438095</v>
+        <v>0.6691488352469595</v>
       </c>
       <c r="D6" t="n">
-        <v>0.494042591850773</v>
+        <v>0.5468422114225763</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4582442168666381</v>
+        <v>0.8338838961013613</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1203877380022312</v>
+        <v>0.716638132807061</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.811333447582505</v>
+        <v>-1.811269448376543</v>
       </c>
       <c r="H6" t="n">
-        <v>1.312600244423219</v>
+        <v>1.312611516551508</v>
       </c>
       <c r="I6" t="n">
-        <v>1.641434124455509</v>
+        <v>1.641429136801486</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4263997673276244</v>
+        <v>-0.4263109581264952</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1771552943768</v>
+        <v>-1.177148006568979</v>
       </c>
       <c r="L6" t="n">
-        <v>915</v>
+        <v>888</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/resultados.xlsx
+++ b/datasets/resultados.xlsx
@@ -485,37 +485,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04289848953589559</v>
+        <v>0.2626014057250683</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1384538233415276</v>
+        <v>0.2871871684006001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5971753034935263</v>
+        <v>0.3338575251049209</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2997400420060883</v>
+        <v>0.5882550552644531</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9051355529908324</v>
+        <v>0.8308272863547894</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.811403147204154</v>
+        <v>-3.347172104590511</v>
       </c>
       <c r="H2" t="n">
-        <v>1.312533327780612</v>
+        <v>1.412348215366406</v>
       </c>
       <c r="I2" t="n">
-        <v>1.641370969343198</v>
+        <v>2.436285666939883</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4266049181231152</v>
+        <v>-1.386788725558269</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.177123572857835</v>
+        <v>-1.538646608579109</v>
       </c>
       <c r="L2" t="n">
-        <v>874</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -525,37 +525,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3173566539875597</v>
+        <v>0.9567201037485323</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2868545494040374</v>
+        <v>0.509962280103854</v>
       </c>
       <c r="D3" t="n">
-        <v>0.787731605552535</v>
+        <v>0.143120648974568</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2280676519740199</v>
+        <v>0.9789099430268807</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9628657425999365</v>
+        <v>0.8147997191544624</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.81125162409968</v>
+        <v>-3.347172635044204</v>
       </c>
       <c r="H3" t="n">
-        <v>1.312527866998524</v>
+        <v>1.412348277457956</v>
       </c>
       <c r="I3" t="n">
-        <v>1.641318757223016</v>
+        <v>2.436285972620521</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4264585693889776</v>
+        <v>-1.386789058649159</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.177082957283175</v>
+        <v>-1.538646710447636</v>
       </c>
       <c r="L3" t="n">
-        <v>880</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -565,37 +565,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3978402639193718</v>
+        <v>0.3058556733530837</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5620282189080513</v>
+        <v>0.05970368903326551</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8070161698698157</v>
+        <v>0.6598244734142776</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01899217805759756</v>
+        <v>0.7068653136094304</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9853537168065982</v>
+        <v>0.3696872557621946</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.811267786774996</v>
+        <v>-3.347172771867048</v>
       </c>
       <c r="H4" t="n">
-        <v>1.312515061780266</v>
+        <v>1.412348463969301</v>
       </c>
       <c r="I4" t="n">
-        <v>1.641307488173511</v>
+        <v>2.436286096488377</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4265008269318374</v>
+        <v>-1.38678927305905</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.177077554027331</v>
+        <v>-1.538646728088736</v>
       </c>
       <c r="L4" t="n">
-        <v>874</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -605,37 +605,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1059012921808319</v>
+        <v>0.05130862864292351</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6590455163622504</v>
+        <v>0.9590187826489549</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7297376894335139</v>
+        <v>0.9034036494465233</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6908461407020068</v>
+        <v>0.1968832590027512</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3366958750227624</v>
+        <v>0.5139696484540538</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.81136516003324</v>
+        <v>-3.347172068455988</v>
       </c>
       <c r="H5" t="n">
-        <v>1.31263028301746</v>
+        <v>1.412347860277762</v>
       </c>
       <c r="I5" t="n">
-        <v>1.64148134186789</v>
+        <v>2.436285553423481</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4263730102491579</v>
+        <v>-1.386788439144374</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.177184778043431</v>
+        <v>-1.538646619264556</v>
       </c>
       <c r="L5" t="n">
-        <v>873</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -645,37 +645,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06357839535486198</v>
+        <v>0.2877417447815279</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6691488352469595</v>
+        <v>0.2894603032682652</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5468422114225763</v>
+        <v>0.1516425884942287</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8338838961013613</v>
+        <v>0.8022285208646371</v>
       </c>
       <c r="F6" t="n">
-        <v>0.716638132807061</v>
+        <v>0.6525621556607418</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.811269448376543</v>
+        <v>-3.347172110297067</v>
       </c>
       <c r="H6" t="n">
-        <v>1.312611516551508</v>
+        <v>1.412348285038999</v>
       </c>
       <c r="I6" t="n">
-        <v>1.641429136801486</v>
+        <v>2.436285688511409</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4263109581264952</v>
+        <v>-1.386788780166252</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.177148006568979</v>
+        <v>-1.538646606381641</v>
       </c>
       <c r="L6" t="n">
-        <v>888</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/resultados.xlsx
+++ b/datasets/resultados.xlsx
@@ -485,37 +485,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2626014057250683</v>
+        <v>0.6216104340573222</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2871871684006001</v>
+        <v>0.1956662598928921</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3338575251049209</v>
+        <v>0.9031481827152088</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5882550552644531</v>
+        <v>0.9030638288601074</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8308272863547894</v>
+        <v>0.6634211027356375</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.347172104590511</v>
+        <v>-1.811323177047153</v>
       </c>
       <c r="H2" t="n">
-        <v>1.412348215366406</v>
+        <v>1.312639112838401</v>
       </c>
       <c r="I2" t="n">
-        <v>2.436285666939883</v>
+        <v>1.641479873439822</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.386788725558269</v>
+        <v>-0.4263118996767787</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.538646608579109</v>
+        <v>-1.177181040047292</v>
       </c>
       <c r="L2" t="n">
-        <v>51</v>
+        <v>912</v>
       </c>
     </row>
     <row r="3">
@@ -525,37 +525,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9567201037485323</v>
+        <v>0.6742232805293642</v>
       </c>
       <c r="C3" t="n">
-        <v>0.509962280103854</v>
+        <v>0.9977857066231026</v>
       </c>
       <c r="D3" t="n">
-        <v>0.143120648974568</v>
+        <v>0.7266045947383825</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9789099430268807</v>
+        <v>0.7238617934030919</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8147997191544624</v>
+        <v>0.2109037028366538</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.347172635044204</v>
+        <v>-1.811344331411226</v>
       </c>
       <c r="H3" t="n">
-        <v>1.412348277457956</v>
+        <v>1.312660424605471</v>
       </c>
       <c r="I3" t="n">
-        <v>2.436285972620521</v>
+        <v>1.641512935695812</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.386789058649159</v>
+        <v>-0.4262916035224095</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.538646710447636</v>
+        <v>-1.177201613286922</v>
       </c>
       <c r="L3" t="n">
-        <v>51</v>
+        <v>899</v>
       </c>
     </row>
     <row r="4">
@@ -565,37 +565,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3058556733530837</v>
+        <v>0.1825021321588147</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05970368903326551</v>
+        <v>0.9337294802802709</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6598244734142776</v>
+        <v>0.359072414351768</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7068653136094304</v>
+        <v>0.5473705463354778</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3696872557621946</v>
+        <v>0.9700603040589423</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.347172771867048</v>
+        <v>-1.811227255927235</v>
       </c>
       <c r="H4" t="n">
-        <v>1.412348463969301</v>
+        <v>1.312571253006767</v>
       </c>
       <c r="I4" t="n">
-        <v>2.436286096488377</v>
+        <v>1.641365926753693</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.38678927305905</v>
+        <v>-0.4263471835616351</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.538646728088736</v>
+        <v>-1.177108554978941</v>
       </c>
       <c r="L4" t="n">
-        <v>50</v>
+        <v>891</v>
       </c>
     </row>
     <row r="5">
@@ -605,37 +605,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05130862864292351</v>
+        <v>0.8630679339249526</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9590187826489549</v>
+        <v>0.8976087838291736</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9034036494465233</v>
+        <v>0.4186440750961156</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1968832590027512</v>
+        <v>0.2790369943143295</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5139696484540538</v>
+        <v>0.3940650821071694</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.347172068455988</v>
+        <v>-1.811262940716975</v>
       </c>
       <c r="H5" t="n">
-        <v>1.412347860277762</v>
+        <v>1.31258405514835</v>
       </c>
       <c r="I5" t="n">
-        <v>2.436285553423481</v>
+        <v>1.64139267079435</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.386788439144374</v>
+        <v>-0.4263588150226914</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.538646619264556</v>
+        <v>-1.177126474367147</v>
       </c>
       <c r="L5" t="n">
-        <v>51</v>
+        <v>904</v>
       </c>
     </row>
     <row r="6">
@@ -645,37 +645,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2877417447815279</v>
+        <v>0.1501348270879282</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2894603032682652</v>
+        <v>0.8819779953287229</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1516425884942287</v>
+        <v>0.4917366930618841</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8022285208646371</v>
+        <v>0.1365992570711146</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6525621556607418</v>
+        <v>0.5298157349227886</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.347172110297067</v>
+        <v>-1.811363175812918</v>
       </c>
       <c r="H6" t="n">
-        <v>1.412348285038999</v>
+        <v>1.312541813822989</v>
       </c>
       <c r="I6" t="n">
-        <v>2.436285688511409</v>
+        <v>1.641369608074715</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.386788780166252</v>
+        <v>-0.4265467267976883</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.538646606381641</v>
+        <v>-1.177120036522683</v>
       </c>
       <c r="L6" t="n">
-        <v>51</v>
+        <v>862</v>
       </c>
     </row>
   </sheetData>
